--- a/product_selector_out/STM32WBA series.xlsx
+++ b/product_selector_out/STM32WBA series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP48"/>
+  <dimension ref="A1:BQ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.953125" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1011,6 +1017,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1353,6 +1360,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1695,6 +1707,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2034,6 +2051,11 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba50kg.pdf</t>
         </is>
       </c>
@@ -2379,6 +2401,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2721,6 +2748,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3063,6 +3095,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3405,6 +3442,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3747,6 +3789,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4086,6 +4133,11 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
@@ -4431,6 +4483,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4773,6 +4830,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5115,6 +5177,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5457,6 +5524,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5799,6 +5871,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6141,6 +6218,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -6483,6 +6565,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6825,6 +6912,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -7167,6 +7259,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -7509,6 +7606,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -7851,6 +7953,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -8190,6 +8297,11 @@
       </c>
       <c r="BP32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
@@ -8535,6 +8647,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -8877,6 +8994,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ34" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -9219,6 +9341,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -9561,6 +9688,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -9903,6 +10035,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -10245,6 +10382,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -10587,6 +10729,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -10929,6 +11076,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -11271,6 +11423,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -11613,6 +11770,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ42" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -11955,6 +12117,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -12294,6 +12461,11 @@
       </c>
       <c r="BP44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba5mmg.pdf</t>
         </is>
       </c>
@@ -12636,6 +12808,11 @@
       </c>
       <c r="BP45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
@@ -12981,6 +13158,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -13323,6 +13505,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ47" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -13665,9 +13852,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ48" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -13690,14 +13882,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -13715,6 +13906,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -13727,6 +13919,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -13786,7 +13979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP48"/>
+  <dimension ref="A1:BQ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13857,6 +14050,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14205,6 +14399,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -14303,6 +14502,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14645,6 +14845,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -14987,6 +15192,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -15324,7 +15534,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
+      <c r="BP14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15671,6 +15886,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -16013,6 +16233,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -16355,6 +16580,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -16697,6 +16927,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -17039,6 +17274,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -17376,7 +17616,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
+      <c r="BP20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17723,6 +17968,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -18065,6 +18315,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -18407,6 +18662,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -18749,6 +19009,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -19091,6 +19356,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -19433,6 +19703,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -19775,6 +20050,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -20117,6 +20397,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -20459,6 +20744,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -20801,6 +21091,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -21143,6 +21438,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -21480,7 +21780,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP32" s="6" t="inlineStr">
+      <c r="BP32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21827,6 +22132,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -22169,6 +22479,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -22511,6 +22826,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -22853,6 +23173,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -23195,6 +23520,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -23537,6 +23867,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -23879,6 +24214,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -24221,6 +24561,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -24563,6 +24908,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -24905,6 +25255,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -25247,6 +25602,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -25584,7 +25944,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP44" s="6" t="inlineStr">
+      <c r="BP44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25926,7 +26291,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP45" s="6" t="inlineStr">
+      <c r="BP45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26273,6 +26643,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -26615,6 +26990,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -26957,11 +27337,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
